--- a/ejemploDatosPeliculas.xlsx
+++ b/ejemploDatosPeliculas.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,16 +10,27 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DE36FD-6D36-4DE7-966B-8007ACA88743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{814A556C-F1FF-47CC-B88D-63D4D8F45CB6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{814A556C-F1FF-47CC-B88D-63D4D8F45CB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="credits" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -31,168 +42,168 @@
     <t>adult</t>
   </si>
   <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>,belongs_to_collection</t>
+  </si>
+  <si>
+    <t>,"{'id': 10194, 'name': 'Toy Story Collection', 'poster_path': '/7G9915LfUQ2lVfwMEEhDsn3kT4B.jpg', 'backdrop_path': '/9FBwqcd9IRruEDUrTdcaafOMKUq.jpg'}"</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>,budget</t>
+  </si>
+  <si>
+    <t>,"30000000"</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>,"42000000"</t>
+  </si>
+  <si>
     <t>,genres</t>
   </si>
   <si>
+    <t>,[{'id': 16, 'name': 'Animation'}, {'id': 35, 'name': 'Comedy'}, {'id': 10751, 'name': 'Family'}]</t>
+  </si>
+  <si>
+    <t>,"[{'id': 53, 'name': 'Thriller'}, {'id': 18, 'name': 'Drama'}]"</t>
+  </si>
+  <si>
     <t>,homepage</t>
   </si>
   <si>
+    <t>,http://toystory.disney.com/toy-story</t>
+  </si>
+  <si>
     <t>,id</t>
   </si>
   <si>
+    <t>,"862"</t>
+  </si>
+  <si>
+    <t>,"80278"</t>
+  </si>
+  <si>
     <t>,imdb_id</t>
   </si>
   <si>
+    <t>,tt0114709</t>
+  </si>
+  <si>
+    <t>,tt1649419</t>
+  </si>
+  <si>
     <t>,original_language</t>
   </si>
   <si>
+    <t>,en</t>
+  </si>
+  <si>
     <t>,original_title</t>
   </si>
   <si>
+    <t>,Toy Story</t>
+  </si>
+  <si>
+    <t>,Lo imposible</t>
+  </si>
+  <si>
     <t>,overview</t>
   </si>
   <si>
+    <t>,"Led by Woody, Andy's toys live happily in his room until Andy's birthday brings Buzz ... the duo eventually learns to put aside their differences."</t>
+  </si>
+  <si>
+    <t>,"In December 2004, close-knit family Maria, Henry and ... unexpected displays of kindness and courage ameliorate their terror."</t>
+  </si>
+  <si>
     <t>,production_companies</t>
   </si>
   <si>
+    <t>,"[{'name': 'Pixar Animation Studios', 'id': 3}]"</t>
+  </si>
+  <si>
+    <t>,"[{'name': 'Summit Entertainment', 'id': 491}, {'name': 'Telecinco Cinema', 'id': 2674}, {'name': 'Apaches Entertainment', 'id': 8111}, {'name': 'Canal+ EspaÃ±a', 'id': 9335}, {'name': 'Instituto de la CinematografÃ­a y de las Artes Audiovisuales (ICAA)', 'id': 9974}, {'name': 'Institut ValenciÃ£ de Cinematografia (IVAC)', 'id': 18309}, {'name': 'Mediaset EspaÃ±a', 'id': 21632}, {'name': 'La Trini', 'id': 53490}, {'name': 'Generalitat Valenciana', 'id': 53491}]"</t>
+  </si>
+  <si>
     <t>,production_countries</t>
   </si>
   <si>
+    <t>,"[{'iso_3166_1': 'US', 'name': 'United States of America'}]"</t>
+  </si>
+  <si>
+    <t>,"[{'iso_3166_1': 'US', 'name': 'United States of America'}, {'iso_3166_1': 'ES', 'name': 'Spain'}]"</t>
+  </si>
+  <si>
     <t>,release_date</t>
   </si>
   <si>
+    <t>,1995-10-30</t>
+  </si>
+  <si>
+    <t>,2012-09-09</t>
+  </si>
+  <si>
     <t>,revenue</t>
   </si>
   <si>
+    <t>,"373554033"</t>
+  </si>
+  <si>
+    <t>,"180274123"</t>
+  </si>
+  <si>
     <t>,runtime</t>
   </si>
   <si>
+    <t>,81.0</t>
+  </si>
+  <si>
+    <t>,113.0</t>
+  </si>
+  <si>
     <t>,spoken_languages</t>
   </si>
   <si>
+    <t>,"[{'iso_639_1': 'en', 'name': 'English'}]"</t>
+  </si>
+  <si>
+    <t>,"[{'iso_639_1': 'en', 'name': 'English'}, {'iso_639_1': 'es', 'name': 'EspaÃ±ol'}, {'iso_639_1': 'sv', 'name': 'svenska'}, {'iso_639_1': 'th', 'name': 'à¸ à¸²à¸©à¸²à¹„à¸—à¸¢'}]"</t>
+  </si>
+  <si>
     <t>,status</t>
   </si>
   <si>
+    <t>,Released</t>
+  </si>
+  <si>
+    <t>,tagline</t>
+  </si>
+  <si>
+    <t>,Nothing is more powerful than the human spirit.</t>
+  </si>
+  <si>
     <t>,title</t>
   </si>
   <si>
-    <t>,belongs_to_collection</t>
-  </si>
-  <si>
-    <t>,budget</t>
-  </si>
-  <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>,"{'id': 10194, 'name': 'Toy Story Collection', 'poster_path': '/7G9915LfUQ2lVfwMEEhDsn3kT4B.jpg', 'backdrop_path': '/9FBwqcd9IRruEDUrTdcaafOMKUq.jpg'}"</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>,[{'id': 16, 'name': 'Animation'}, {'id': 35, 'name': 'Comedy'}, {'id': 10751, 'name': 'Family'}]</t>
-  </si>
-  <si>
-    <t>,"30000000"</t>
-  </si>
-  <si>
-    <t>,http://toystory.disney.com/toy-story</t>
-  </si>
-  <si>
-    <t>,tt0114709</t>
-  </si>
-  <si>
-    <t>,en</t>
-  </si>
-  <si>
-    <t>,Toy Story</t>
-  </si>
-  <si>
-    <t>,"[{'name': 'Pixar Animation Studios', 'id': 3}]"</t>
-  </si>
-  <si>
-    <t>,"[{'iso_3166_1': 'US', 'name': 'United States of America'}]"</t>
-  </si>
-  <si>
-    <t>,1995-10-30</t>
-  </si>
-  <si>
-    <t>,"373554033"</t>
-  </si>
-  <si>
-    <t>,81.0</t>
-  </si>
-  <si>
-    <t>,"[{'iso_639_1': 'en', 'name': 'English'}]"</t>
-  </si>
-  <si>
-    <t>,Released</t>
-  </si>
-  <si>
-    <t>,"862"</t>
-  </si>
-  <si>
-    <t>,tagline</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>,"Led by Woody, Andy's toys live happily in his room until Andy's birthday brings Buzz ... the duo eventually learns to put aside their differences."</t>
-  </si>
-  <si>
-    <t>,"42000000"</t>
-  </si>
-  <si>
-    <t>,"[{'id': 53, 'name': 'Thriller'}, {'id': 18, 'name': 'Drama'}]"</t>
-  </si>
-  <si>
-    <t>,"80278"</t>
-  </si>
-  <si>
-    <t>,tt1649419</t>
-  </si>
-  <si>
-    <t>,Lo imposible</t>
-  </si>
-  <si>
-    <t>,"In December 2004, close-knit family Maria, Henry and ... unexpected displays of kindness and courage ameliorate their terror."</t>
-  </si>
-  <si>
-    <t>,"[{'name': 'Summit Entertainment', 'id': 491}, {'name': 'Telecinco Cinema', 'id': 2674}, {'name': 'Apaches Entertainment', 'id': 8111}, {'name': 'Canal+ EspaÃ±a', 'id': 9335}, {'name': 'Instituto de la CinematografÃ­a y de las Artes Audiovisuales (ICAA)', 'id': 9974}, {'name': 'Institut ValenciÃ£ de Cinematografia (IVAC)', 'id': 18309}, {'name': 'Mediaset EspaÃ±a', 'id': 21632}, {'name': 'La Trini', 'id': 53490}, {'name': 'Generalitat Valenciana', 'id': 53491}]"</t>
-  </si>
-  <si>
-    <t>,"[{'iso_3166_1': 'US', 'name': 'United States of America'}, {'iso_3166_1': 'ES', 'name': 'Spain'}]"</t>
-  </si>
-  <si>
-    <t>,2012-09-09</t>
-  </si>
-  <si>
-    <t>,"180274123"</t>
-  </si>
-  <si>
-    <t>,113.0</t>
-  </si>
-  <si>
-    <t>,"[{'iso_639_1': 'en', 'name': 'English'}, {'iso_639_1': 'es', 'name': 'EspaÃ±ol'}, {'iso_639_1': 'sv', 'name': 'svenska'}, {'iso_639_1': 'th', 'name': 'à¸ à¸²à¸©à¸²à¹„à¸—à¸¢'}]"</t>
-  </si>
-  <si>
-    <t>,Nothing is more powerful than the human spirit.</t>
-  </si>
-  <si>
     <t>,The Impossible</t>
   </si>
   <si>
     <t>cast</t>
   </si>
   <si>
+    <t>[{'cast_id': 14, 'character': 'Woody (voice)', 'credit_id': '52fe4284c3a36847f8024f95', 'gender': 2, 'id': 31, 'name': 'Tom Hanks', 'order': 0, 'profile_path': '/pQFoyx7rp09CJTAb932F2g8Nlho.jpg'}, {'cast_id': 15, 'character': 'Buzz Lightyear (voice)', 'credit_id': '52fe4284c3a36847f8024f99', 'gender': 2, 'id': 12898, 'name': 'Tim Allen', 'order': 1, 'profile_path': '/uX2xVf6pMmPepxnvFWyBtjexzgY.jpg'}, {'cast_id': 16, 'character': 'Mr. Potato Head (voice)', 'credit_id': '52fe4284c3a36847f8024f9d', 'gender': 2, 'id': 7167, 'name': 'Don Rickles', 'order': 2, 'profile_path': '/h5BcaDMPRVLHLDzbQavec4xfSdt.jpg'}, {'cast_id': 17, 'character': 'Slinky Dog (voice)', 'credit_id': '52fe4284c3a36847f8024fa1', 'gender': 2, 'id': 12899, 'name': 'Jim Varney', 'order': 3, 'profile_path': '/eIo2jVVXYgjDtaHoF19Ll9vtW7h.jpg'}, {'cast_id': 18, 'character': 'Rex (voice)', 'credit_id': '52fe4284c3a36847f8024fa5', 'gender': 2, 'id': 12900, 'name': 'Wallace Shawn', 'order': 4, 'profile_path': '/oGE6JqPP2xH4tNORKNqxbNPYi7u.jpg'}, {'cast_id': 19, 'character': 'Hamm (voice)', 'credit_id': '52fe4284c3a36847f8024fa9', 'gender': 2, 'id': 7907, 'name': 'John Ratzenberger', 'order': 5, 'profile_path': '/yGechiKWL6TJDfVE2KPSJYqdMsY.jpg'}, {'cast_id': 20, 'character': 'Bo Peep (voice)', 'credit_id': '52fe4284c3a36847f8024fad', 'gender': 1, 'id': 8873, 'name': 'Annie Potts', 'order': 6, 'profile_path': '/eryXT84RL41jHSJcMy4kS3u9y6w.jpg'}, {'cast_id': 26, 'character': 'Andy (voice)', 'credit_id': '52fe4284c3a36847f8024fc1', 'gender': 0, 'id': 1116442, 'name': 'John Morris', 'order': 7, 'profile_path': '/vYGyvK4LzeaUCoNSHtsuqJUY15M.jpg'}, {'cast_id': 22, 'character': 'Sid (voice)', 'credit_id': '52fe4284c3a36847f8024fb1', 'gender': 2, 'id': 12901, 'name': 'Erik von Detten', 'order': 8, 'profile_path': '/twnF1ZaJ1FUNUuo6xLXwcxjayBE.jpg'}, {'cast_id': 23, 'character': 'Mrs. Davis (voice)', 'credit_id': '52fe4284c3a36847f8024fb5', 'gender': 1, 'id': 12133, 'name': 'Laurie Metcalf', 'order': 9, 'profile_path': '/unMMIT60eoBM2sN2nyR7EZ2BvvD.jpg'}, {'cast_id': 24, 'character': 'Sergeant (voice)', 'credit_id': '52fe4284c3a36847f8024fb9', 'gender': 2, 'id': 8655, 'name': 'R. Lee Ermey', 'order': 10, 'profile_path': '/r8GBqFBjypLUP9VVqDqfZ7wYbSs.jpg'}, {'cast_id': 25, 'character': 'Hannah (voice)', 'credit_id': '52fe4284c3a36847f8024fbd', 'gender': 1, 'id': 12903, 'name': 'Sarah Freeman', 'order': 11, 'profile_path': None}, {'cast_id': 27, 'character': 'TV Announcer (voice)', 'credit_id': '52fe4284c3a36847f8024fc5', 'gender': 2, 'id': 37221, 'name': 'Penn Jillette', 'order': 12, 'profile_path': '/zmAaXUdx12NRsssgHbk1T31j2x9.jpg'}]</t>
+  </si>
+  <si>
     <t>,crew</t>
   </si>
   <si>
-    <t>[{'cast_id': 14, 'character': 'Woody (voice)', 'credit_id': '52fe4284c3a36847f8024f95', 'gender': 2, 'id': 31, 'name': 'Tom Hanks', 'order': 0, 'profile_path': '/pQFoyx7rp09CJTAb932F2g8Nlho.jpg'}, {'cast_id': 15, 'character': 'Buzz Lightyear (voice)', 'credit_id': '52fe4284c3a36847f8024f99', 'gender': 2, 'id': 12898, 'name': 'Tim Allen', 'order': 1, 'profile_path': '/uX2xVf6pMmPepxnvFWyBtjexzgY.jpg'}, {'cast_id': 16, 'character': 'Mr. Potato Head (voice)', 'credit_id': '52fe4284c3a36847f8024f9d', 'gender': 2, 'id': 7167, 'name': 'Don Rickles', 'order': 2, 'profile_path': '/h5BcaDMPRVLHLDzbQavec4xfSdt.jpg'}, {'cast_id': 17, 'character': 'Slinky Dog (voice)', 'credit_id': '52fe4284c3a36847f8024fa1', 'gender': 2, 'id': 12899, 'name': 'Jim Varney', 'order': 3, 'profile_path': '/eIo2jVVXYgjDtaHoF19Ll9vtW7h.jpg'}, {'cast_id': 18, 'character': 'Rex (voice)', 'credit_id': '52fe4284c3a36847f8024fa5', 'gender': 2, 'id': 12900, 'name': 'Wallace Shawn', 'order': 4, 'profile_path': '/oGE6JqPP2xH4tNORKNqxbNPYi7u.jpg'}, {'cast_id': 19, 'character': 'Hamm (voice)', 'credit_id': '52fe4284c3a36847f8024fa9', 'gender': 2, 'id': 7907, 'name': 'John Ratzenberger', 'order': 5, 'profile_path': '/yGechiKWL6TJDfVE2KPSJYqdMsY.jpg'}, {'cast_id': 20, 'character': 'Bo Peep (voice)', 'credit_id': '52fe4284c3a36847f8024fad', 'gender': 1, 'id': 8873, 'name': 'Annie Potts', 'order': 6, 'profile_path': '/eryXT84RL41jHSJcMy4kS3u9y6w.jpg'}, {'cast_id': 26, 'character': 'Andy (voice)', 'credit_id': '52fe4284c3a36847f8024fc1', 'gender': 0, 'id': 1116442, 'name': 'John Morris', 'order': 7, 'profile_path': '/vYGyvK4LzeaUCoNSHtsuqJUY15M.jpg'}, {'cast_id': 22, 'character': 'Sid (voice)', 'credit_id': '52fe4284c3a36847f8024fb1', 'gender': 2, 'id': 12901, 'name': 'Erik von Detten', 'order': 8, 'profile_path': '/twnF1ZaJ1FUNUuo6xLXwcxjayBE.jpg'}, {'cast_id': 23, 'character': 'Mrs. Davis (voice)', 'credit_id': '52fe4284c3a36847f8024fb5', 'gender': 1, 'id': 12133, 'name': 'Laurie Metcalf', 'order': 9, 'profile_path': '/unMMIT60eoBM2sN2nyR7EZ2BvvD.jpg'}, {'cast_id': 24, 'character': 'Sergeant (voice)', 'credit_id': '52fe4284c3a36847f8024fb9', 'gender': 2, 'id': 8655, 'name': 'R. Lee Ermey', 'order': 10, 'profile_path': '/r8GBqFBjypLUP9VVqDqfZ7wYbSs.jpg'}, {'cast_id': 25, 'character': 'Hannah (voice)', 'credit_id': '52fe4284c3a36847f8024fbd', 'gender': 1, 'id': 12903, 'name': 'Sarah Freeman', 'order': 11, 'profile_path': None}, {'cast_id': 27, 'character': 'TV Announcer (voice)', 'credit_id': '52fe4284c3a36847f8024fc5', 'gender': 2, 'id': 37221, 'name': 'Penn Jillette', 'order': 12, 'profile_path': '/zmAaXUdx12NRsssgHbk1T31j2x9.jpg'}]</t>
-  </si>
-  <si>
     <t>,"[{'credit_id': '52fe4284c3a36847f8024f49', 'department': 'Directing', 'gender': 2, 'id': 7879, 'job': 'Director', 'name': 'John Lasseter', 'profile_path': '/7EdqiNbr4FRjIhKHyPPdFfEEEFG.jpg'}, {'credit_id': '52fe4284c3a36847f8024f4f', 'department': 'Writing', 'gender': 2, 'id': 12891, 'job': 'Screenplay', 'name': 'Joss Whedon', 'profile_path': '/dTiVsuaTVTeGmvkhcyJvKp2A5kr.jpg'}, {'credit_id': '52fe4284c3a36847f8024f55', 'department': 'Writing', 'gender': 2, 'id': 7, 'job': 'Screenplay', 'name': 'Andrew Stanton', 'profile_path': '/pvQWsu0qc8JFQhMVJkTHuexUAa1.jpg'}, {'credit_id': '52fe4284c3a36847f8024f5b', 'department': 'Writing', 'gender': 2, 'id': 12892, 'job': 'Screenplay', 'name': 'Joel Cohen', 'profile_path': '/dAubAiZcvKFbboWlj7oXOkZnTSu.jpg'}, {'credit_id': '52fe4284c3a36847f8024f61', 'department': 'Writing', 'gender': 0, 'id': 12893, 'job': 'Screenplay', 'name': 'Alec Sokolow', 'profile_path': '/v79vlRYi94BZUQnkkyznbGUZLjT.jpg'}, {'credit_id': '52fe4284c3a36847f8024f67', 'department': 'Production', 'gender': 1, 'id': 12894, 'job': 'Producer', 'name': 'Bonnie Arnold', 'profile_path': None}, {'credit_id': '52fe4284c3a36847f8024f6d', 'department': 'Production', 'gender': 0, 'id': 12895, 'job': 'Executive Producer', 'name': 'Ed Catmull', 'profile_path': None}, {'credit_id': '52fe4284c3a36847f8024f73', 'department': 'Production', 'gender': 2, 'id': 12896, 'job': 'Producer', 'name': 'Ralph Guggenheim', 'profile_path': None}, {'credit_id': '52fe4284c3a36847f8024f79', 'department': 'Production', 'gender': 2, 'id': 12897, 'job': 'Executive Producer', 'name': 'Steve Jobs', 'profile_path': '/mOMP3SwD5qWQSR0ldCIByd3guTV.jpg'}, {'credit_id': '52fe4284c3a36847f8024f8b', 'department': 'Editing', 'gender': 2, 'id': 8, 'job': 'Editor', 'name': 'Lee Unkrich', 'profile_path': '/bdTCCXjgOV3YyaNmLGYGOxFQMOc.jpg'}, {'credit_id': '52fe4284c3a36847f8024f91', 'department': 'Art', 'gender': 2, 'id': 7883, 'job': 'Art Direction', 'name': 'Ralph Eggleston', 'profile_path': '/uUfcGKDsKO1aROMpXRs67Hn6RvR.jpg'}, {'credit_id': '598331bf925141421201044b', 'department': 'Editing', 'gender': 2, 'id': 1168870, 'job': 'Editor', 'name': 'Robert Gordon', 'profile_path': None}, {'credit_id': '5892168cc3a36809660095f9', 'department': 'Sound', 'gender': 0, 'id': 1552883, 'job': 'Foley Editor', 'name': 'Mary Helen Leasman', 'profile_path': None}, {'credit_id': '5531824d9251415289000945', 'department': 'Visual Effects', 'gender': 0, 'id': 1453514, 'job': 'Animation', 'name': 'Kim Blanchette', 'profile_path': None}, {'credit_id': '589215969251412dcb009bf6', 'department': 'Sound', 'gender': 0, 'id': 1414182, 'job': 'ADR Editor', 'name': 'Marilyn McCoppen', 'profile_path': None}, {'credit_id': '589217099251412dc500a018', 'department': 'Sound', 'gender': 2, 'id': 7885, 'job': 'Orchestrator', 'name': 'Randy Newman', 'profile_path': '/w0JzfoiM25nrnxYOzosPHRq6mlE.jpg'}, {'credit_id': '5693e6b29251417b0e0000e3', 'department': 'Editing', 'gender': 0, 'id': 1429549, 'job': 'Color Timer', 'name': 'Dale E. Grahn', 'profile_path': None}, {'credit_id': '572e2522c3a36869e6001a9c', 'department': 'Visual Effects', 'gender': 0, 'id': 7949, 'job': 'CG Painter', 'name': 'Robin Cooper', 'profile_path': None}, {'credit_id': '574f12309251415ca1000012', 'department': 'Writing', 'gender': 2, 'id': 7879, 'job': 'Original Story', 'name': 'John Lasseter', 'profile_path': '/7EdqiNbr4FRjIhKHyPPdFfEEEFG.jpg'}, {'credit_id': '574f1240c3a3682e7300001c', 'department': 'Writing', 'gender': 2, 'id': 12890, 'job': 'Original Story', 'name': 'Pete Docter', 'profile_path': '/r6ngPgnReA3RHmKjmSoVsc6Awjp.jpg'}, {'credit_id': '574f12519251415c92000015', 'department': 'Writing', 'gender': 0, 'id': 7911, 'job': 'Original Story', 'name': 'Joe Ranft', 'profile_path': '/f1BoWC2JbCcfP1e5hKfGsxkHzVU.jpg'}, {'credit_id': '574f12cec3a3682e82000022', 'department': 'Crew', 'gender': 0, 'id': 1629419, 'job': 'Post Production Supervisor', 'name': 'Patsy Bouge', 'profile_path': None}, {'credit_id': '574f14f19251415ca1000082', 'department': 'Art', 'gender': 0, 'id': 7961, 'job': 'Sculptor', 'name': 'Norm DeCarlo', 'profile_path': None}, {'credit_id': '5751ae4bc3a3683772002b7f', 'department': 'Visual Effects', 'gender': 2, 'id': 12905, 'job': 'Animation Director', 'name': 'Ash Brannon', 'profile_path': '/6ueWgPEEBHvS3De2BHYQnYjRTig.jpg'}, {'credit_id': '5891edbe9251412dc5007cd6', 'department': 'Sound', 'gender': 2, 'id': 7885, 'job': 'Music', 'name': 'Randy Newman', 'profile_path': '/w0JzfoiM25nrnxYOzosPHRq6mlE.jpg'}, {'credit_id': '589213d39251412dc8009832', 'department': 'Directing', 'gender': 0, 'id': 1748707, 'job': 'Layout', 'name': 'Roman Figun', 'profile_path': None}, {'credit_id': '5892173dc3a3680968009351', 'department': 'Sound', 'gender': 2, 'id': 4949, 'job': 'Orchestrator', 'name': 'Don Davis', 'profile_path': None}, {'credit_id': '589217cec3a3686b0a0052ba', 'department': 'Sound', 'gender': 0, 'id': 1372885, 'job': 'Music Editor', 'name': 'James Flamberg', 'profile_path': None}, {'credit_id': '58921831c3a3686348004a64', 'department': 'Editing', 'gender': 0, 'id': 1739962, 'job': 'Negative Cutter', 'name': 'Mary Beth Smith', 'profile_path': None}, {'credit_id': '58921838c3a36809700096c0', 'department': 'Editing', 'gender': 0, 'id': 1748513, 'job': 'Negative Cutter', 'name': 'Rick Mackay', 'profile_path': None}, {'credit_id': '589218429251412dd1009d1b', 'department': 'Art', 'gender': 0, 'id': 1458006, 'job': 'Title Designer', 'name': 'Susan Bradley', 'profile_path': None}, {'credit_id': '5891ed99c3a3680966007670', 'department': 'Crew', 'gender': 0, 'id': 1748557, 'job': 'Supervising Technical Director', 'name': 'William Reeves', 'profile_path': None}, {'credit_id': '5891edcec3a3686b0a002eb2', 'department': 'Sound', 'gender': 2, 'id': 7885, 'job': 'Songs', 'name': 'Randy Newman', 'profile_path': '/w0JzfoiM25nrnxYOzosPHRq6mlE.jpg'}, {'credit_id': '5891edf9c3a36809700075e6', 'department': 'Writing', 'gender': 2, 'id': 7, 'job': 'Original Story', 'name': 'Andrew Stanton', 'profile_path': '/pvQWsu0qc8JFQhMVJkTHuexUAa1.jpg'}, {'credit_id': '58920f0b9251412dd7009104', 'department': 'Crew', 'gender': 2, 'id': 12890, 'job': 'Supervising Animator', 'name': 'Pete Docter', 'profile_path': '/r6ngPgnReA3RHmKjmSoVsc6Awjp.jpg'}, {'credit_id': '58920f1fc3a3680977009021', 'department': 'Sound', 'gender': 2, 'id': 2216, 'job': 'Sound Designer', 'name': 'Gary Rydstrom', 'profile_path': '/jZpr1nVfO7lldWI0YtmP1FGw7Rj.jpg'}, {'credit_id': '58920f389251412dd700912d', 'department': 'Production', 'gender': 0, 'id': 12909, 'job': 'Production Supervisor', 'name': 'Karen Robert Jackson', 'profile_path': None}, {'credit_id': '58920fbd9251412dcb00969c', 'department': 'Crew', 'gender': 0, 'id': 953331, 'job': 'Executive Music Producer', 'name': 'Chris Montan', 'profile_path': None}, {'credit_id': '589210069251412dd7009219', 'department': 'Visual Effects', 'gender': 0, 'id': 7893, 'job': 'Animation Director', 'name': 'Rich Quade', 'profile_path': None}, {'credit_id': '589210329251412dcd00943b', 'department': 'Visual Effects', 'gender': 0, 'id': 8025, 'job': 'Animation', 'name': 'Michael Berenstein', 'profile_path': None}, {'credit_id': '5892103bc3a368096a009180', 'department': 'Visual Effects', 'gender': 0, 'id': 78009, 'job': 'Animation', 'name': 'Colin Brady', 'profile_path': None}, {'credit_id': '5892105dc3a3680968008db2', 'department': 'Visual Effects', 'gender': 0, 'id': 1748682, 'job': 'Animation', 'name': 'Davey Crockett Feiten', 'profile_path': None}, {'credit_id': '589210669251412dcd009466', 'department': 'Visual Effects', 'gender': 0, 'id': 1454030, 'job': 'Animation', 'name': 'Angie Glocka', 'profile_path': None}, {'credit_id': '5892107c9251412dd1009613', 'department': 'Visual Effects', 'gender': 0, 'id': 1748683, 'job': 'Animation', 'name': 'Rex Grignon', 'profile_path': None}, {'credit_id': '5892108ac3a3680973008d3f', 'department': 'Visual Effects', 'gender': 0, 'id': 1748684, 'job': 'Animation', 'name': 'Tom K. Gurney', 'profile_path': None}, {'credit_id': '58921093c3a3686348004477', 'department': 'Visual Effects', 'gender': 2, 'id': 8029, 'job': 'Animation', 'name': 'Jimmy Hayward', 'profile_path': '/lTDRpudEY7BDwTefXbXzMlmb0ui.jpg'}, {'credit_id': '5892109b9251412dcd0094b0', 'department': 'Visual Effects', 'gender': 0, 'id': 1426773, 'job': 'Animation', 'name': 'Hal T. Hickel', 'profile_path': None}, {'credit_id': '589210a29251412dc5009a29', 'department': 'Visual Effects', 'gender': 0, 'id': 8035, 'job': 'Animation', 'name': 'Karen Kiser', 'profile_path': None}, {'credit_id': '589210ccc3a3680977009191', 'department': 'Visual Effects', 'gender': 0, 'id': 1748688, 'job': 'Animation', 'name': 'Anthony B. LaMolinara', 'profile_path': None}, {'credit_id': '589210d7c3a3686b0a004c1f', 'department': 'Visual Effects', 'gender': 0, 'id': 587314, 'job': 'Animation', 'name': 'Guionne Leroy', 'profile_path': None}, {'credit_id': '589210e1c3a36809770091a7', 'department': 'Visual Effects', 'gender': 2, 'id': 7918, 'job': 'Animation', 'name': 'Bud Luckey', 'profile_path': '/pcCh7G19FKMNijmPQg1PMH1btic.jpg'}, {'credit_id': '589210ee9251412dc200978a', 'department': 'Visual Effects', 'gender': 0, 'id': 1748689, 'job': 'Animation', 'name': 'Les Major', 'profile_path': None}, {'credit_id': '589210fa9251412dc8009595', 'department': 'Visual Effects', 'gender': 2, 'id': 7892, 'job': 'Animation', 'name': 'Glenn McQueen', 'profile_path': None}, {'credit_id': '589211029251412dc8009598', 'department': 'Visual Effects', 'gender': 0, 'id': 555795, 'job': 'Animation', 'name': 'Mark Oftedal', 'profile_path': None}, {'credit_id': '5892110b9251412dc800959d', 'department': 'Visual Effects', 'gender': 2, 'id': 7882, 'job': 'Animation', 'name': 'Jeff Pidgeon', 'profile_path': '/yLddkg5HcgbJg00cS13GVBnP0HY.jpg'}, {'credit_id': '58921113c3a36863480044e4', 'department': 'Visual Effects', 'gender': 0, 'id': 8017, 'job': 'Animation', 'name': 'Jeff Pratt', 'profile_path': None}, {'credit_id': '5892111c9251412dcb0097e9', 'department': 'Visual Effects', 'gender': 0, 'id': 1184140, 'job': 'Animation', 'name': 'Steve Rabatich', 'profile_path': None}, {'credit_id': '58921123c3a36809700090f6', 'department': 'Visual Effects', 'gender': 0, 'id': 8049, 'job': 'Animation', 'name': 'Roger Rose', 'profile_path': None}, {'credit_id': '5892112b9251412dcb0097fb', 'department': 'Visual Effects', 'gender': 0, 'id': 1509559, 'job': 'Animation', 'name': 'Steve Segal', 'profile_path': None}, {'credit_id': '589211349251412dc80095c3', 'department': 'Visual Effects', 'gender': 0, 'id': 1748691, 'job': 'Animation', 'name': 'Doug Sheppeck', 'profile_path': None}, {'credit_id': '5892113cc3a3680970009106', 'department': 'Visual Effects', 'gender': 0, 'id': 8050, 'job': 'Animation', 'name': 'Alan Sperling', 'profile_path': None}, {'credit_id': '58921148c3a3686b0a004c99', 'department': 'Visual Effects', 'gender': 0, 'id': 8010, 'job': 'Animation', 'name': 'Doug Sweetland', 'profile_path': None}, {'credit_id': '58921150c3a3680966009125', 'department': 'Visual Effects', 'gender': 0, 'id': 8044, 'job': 'Animation', 'name': 'David Tart', 'profile_path': None}, {'credit_id': '589211629251412dc5009b00', 'department': 'Visual Effects', 'gender': 0, 'id': 1454034, 'job': 'Animation', 'name': 'Ken Willard', 'profile_path': None}, {'credit_id': '589211c1c3a3686b0a004d28', 'department': 'Visual Effects', 'gender': 0, 'id': 7887, 'job': 'Visual Effects Supervisor', 'name': 'Thomas Porter', 'profile_path': None}, {'credit_id': '589211d4c3a3680968008ed9', 'department': 'Visual Effects', 'gender': 0, 'id': 1406878, 'job': 'Visual Effects', 'name': 'Mark Thomas Henne', 'profile_path': None}, {'credit_id': '589211f59251412dd4008e65', 'department': 'Visual Effects', 'gender': 0, 'id': 1748698, 'job': 'Visual Effects', 'name': 'Oren Jacob', 'profile_path': None}, {'credit_id': '58921242c3a368096a00939b', 'department': 'Visual Effects', 'gender': 0, 'id': 1748699, 'job': 'Visual Effects', 'name': 'Darwyn Peachey', 'profile_path': None}, {'credit_id': '5892124b9251412dc5009bd2', 'department': 'Visual Effects', 'gender': 0, 'id': 1748701, 'job': 'Visual Effects', 'name': 'Mitch Prater', 'profile_path': None}, {'credit_id': '58921264c3a3686b0a004dbf', 'department': 'Visual Effects', 'gender': 0, 'id': 1748703, 'job': 'Visual Effects', 'name': 'Brian M. Rosen', 'profile_path': None}, {'credit_id': '589212709251412dcd009676', 'department': 'Lighting', 'gender': 1, 'id': 12912, 'job': 'Lighting Supervisor', 'name': 'Sharon Calahan', 'profile_path': None}, {'credit_id': '5892127fc3a3686b0a004de5', 'department': 'Lighting', 'gender': 0, 'id': 7899, 'job': 'Lighting Supervisor', 'name': 'Galyn Susman', 'profile_path': None}, {'credit_id': '589212cdc3a3680970009268', 'department': 'Visual Effects', 'gender': 0, 'id': 12915, 'job': 'CG Painter', 'name': 'William Cone', 'profile_path': None}, {'credit_id': '5892130f9251412dc8009791', 'department': 'Art', 'gender': 0, 'id': 1748705, 'job': 'Sculptor', 'name': 'Shelley Daniels Lekven', 'profile_path': None}, {'credit_id': '5892131c9251412dd4008f4c', 'department': 'Visual Effects', 'gender': 2, 'id': 7889, 'job': 'Character Designer', 'name': 'Bob Pauley', 'profile_path': None}, {'credit_id': '589213249251412dd100987b', 'department': 'Visual Effects', 'gender': 2, 'id': 7918, 'job': 'Character Designer', 'name': 'Bud Luckey', 'profile_path': '/pcCh7G19FKMNijmPQg1PMH1btic.jpg'}, {'credit_id': '5892132b9251412dc80097b1', 'department': 'Visual Effects', 'gender': 2, 'id': 7, 'job': 'Character Designer', 'name': 'Andrew Stanton', 'profile_path': '/pvQWsu0qc8JFQhMVJkTHuexUAa1.jpg'}, {'credit_id': '58921332c3a368634800467b', 'department': 'Visual Effects', 'gender': 0, 'id': 12915, 'job': 'Character Designer', 'name': 'William Cone', 'profile_path': None}, {'credit_id': '5892135f9251412dd4008f90', 'department': 'Visual Effects', 'gender': 0, 'id': 1748706, 'job': 'Character Designer', 'name': 'Steve Johnson', 'profile_path': None}, {'credit_id': '58921384c3a3680973008fd4', 'department': 'Visual Effects', 'gender': 0, 'id': 1176752, 'job': 'Character Designer', 'name': 'Dan Haskett', 'profile_path': None}, {'credit_id': '5892138e9251412dc20099fc', 'department': 'Visual Effects', 'gender': 0, 'id': 1088034, 'job': 'Character Designer', 'name': 'Tom Holloway', 'profile_path': '/a0r0T2usTBpgMI5aZbRBDW1fTl8.jpg'}, {'credit_id': '58921395c3a368097700942f', 'department': 'Visual Effects', 'gender': 0, 'id': 1447465, 'job': 'Character Designer', 'name': 'Jean Gillmore', 'profile_path': None}, {'credit_id': '589213e2c3a3680973009026', 'department': 'Directing', 'gender': 0, 'id': 1748709, 'job': 'Layout', 'name': 'DesirÃ©e Mourad', 'profile_path': None}, {'credit_id': '589214099251412dc5009d57', 'department': 'Art', 'gender': 0, 'id': 1748710, 'job': 'Set Dresser', 'name': ""Kelly O'Connell"", 'profile_path': None}, {'credit_id': '58921411c3a3686b0a004f70', 'department': 'Art', 'gender': 0, 'id': 1443471, 'job': 'Set Dresser', 'name': 'Sonoko Konishi', 'profile_path': None}, {'credit_id': '58921434c3a368096a00956e', 'department': 'Art', 'gender': 0, 'id': 1748711, 'job': 'Set Dresser', 'name': 'Ann M. Rockwell', 'profile_path': None}, {'credit_id': '5892144ac3a36809680090de', 'department': 'Editing', 'gender': 0, 'id': 1748712, 'job': 'Editorial Manager', 'name': 'Julie M. McDonald', 'profile_path': None}, {'credit_id': '58921479c3a368096800910f', 'department': 'Editing', 'gender': 0, 'id': 1589729, 'job': 'Assistant Editor', 'name': 'Robin Lee', 'profile_path': None}, {'credit_id': '5892148b9251412dd10099cc', 'department': 'Editing', 'gender': 0, 'id': 1748716, 'job': 'Assistant Editor', 'name': 'Tom Freeman', 'profile_path': None}, {'credit_id': '589214959251412dcb009b1f', 'department': 'Editing', 'gender': 0, 'id': 1748717, 'job': 'Assistant Editor', 'name': 'Ada Cochavi', 'profile_path': None}, {'credit_id': '5892149ec3a3686348004798', 'department': 'Editing', 'gender': 0, 'id': 1336438, 'job': 'Assistant Editor', 'name': 'Dana Mulligan', 'profile_path': None}, {'credit_id': '589214adc3a368096a0095db', 'department': 'Editing', 'gender': 0, 'id': 1748718, 'job': 'Editorial Coordinator', 'name': 'Deirdre Morrison', 'profile_path': None}, {'credit_id': '589214c7c3a368097700952b', 'department': 'Production', 'gender': 0, 'id': 1748719, 'job': 'Production Coordinator', 'name': 'Lori Lombardo', 'profile_path': None}, {'credit_id': '589214cec3a368096a009603', 'department': 'Production', 'gender': 0, 'id': 1748720, 'job': 'Production Coordinator', 'name': 'Ellen Devine', 'profile_path': None}, {'credit_id': '589214e39251412dc8009904', 'department': 'Crew', 'gender': 0, 'id': 1468014, 'job': 'Unit Publicist', 'name': 'Lauren Beth Strogoff', 'profile_path': None}, {'credit_id': '58921544c3a3686b0a00507d', 'department': 'Sound', 'gender': 2, 'id': 2216, 'job': 'Sound Re-Recording Mixer', 'name': 'Gary Rydstrom', 'profile_path': '/jZpr1nVfO7lldWI0YtmP1FGw7Rj.jpg'}, {'credit_id': '5892154c9251412dd1009a56', 'department': 'Sound', 'gender': 0, 'id': 1425978, 'job': 'Sound Re-Recording Mixer', 'name': 'Gary Summers', 'profile_path': None}, {'credit_id': '58921555c3a36809680091bd', 'department': 'Sound', 'gender': 2, 'id': 8276, 'job': 'Supervising Sound Editor', 'name': 'Tim Holland', 'profile_path': None}, {'credit_id': '589215c39251412dcb009c12', 'department': 'Sound', 'gender': 0, 'id': 7069, 'job': 'Sound Effects Editor', 'name': 'Pat Jackson', 'profile_path': None}, {'credit_id': '58921698c3a368096a009788', 'department': 'Crew', 'gender': 2, 'id': 15894, 'job': 'Sound Design Assistant', 'name': 'Tom Myers', 'profile_path': None}, {'credit_id': '589216a89251412dc2009ca4', 'department': 'Sound', 'gender': 0, 'id': 1414177, 'job': 'Assistant Sound Editor', 'name': 'J.R. Grubbs', 'profile_path': None}, {'credit_id': '589216c19251412dc2009cb9', 'department': 'Sound', 'gender': 1, 'id': 1748724, 'job': 'Assistant Sound Editor', 'name': 'Susan Sanford', 'profile_path': None}, {'credit_id': '589216ccc3a3680973009274', 'department': 'Sound', 'gender': 0, 'id': 1748725, 'job': 'Assistant Sound Editor', 'name': 'Susan Popovic', 'profile_path': None}, {'credit_id': '589216d79251412dc8009aa0', 'department': 'Sound', 'gender': 0, 'id': 8067, 'job': 'Assistant Sound Editor', 'name': 'Dan Engstrom', 'profile_path': None}, {'credit_id': '589216e49251412dcd009a4f', 'department': 'Production', 'gender': 1, 'id': 7902, 'job': 'Casting Consultant', 'name': 'Ruth Lambert', 'profile_path': None}, {'credit_id': '589216f39251412dc2009cf3', 'department': 'Production', 'gender': 0, 'id': 84493, 'job': 'ADR Voice Casting', 'name': 'Mickie McGowan', 'profile_path': '/k7TjJBfINsg8vLQxJwos6XObAD6.jpg'}]"</t>
   </si>
   <si>
@@ -202,29 +213,29 @@
     <t>{'credit_id': '52fe4284c3a36847f8024f49', 'department': 'Directing', 'gender': 2, 'id': 7879, 'job': 'Director', 'name': 'John Lasseter', 'profile_path': '/7EdqiNbr4FRjIhKHyPPdFfEEEFG.jpg'},</t>
   </si>
   <si>
+    <t>usuarioID</t>
+  </si>
+  <si>
+    <t>movieID</t>
+  </si>
+  <si>
     <t>rating</t>
   </si>
   <si>
-    <t>movieID</t>
-  </si>
-  <si>
     <t>,5.0</t>
   </si>
   <si>
+    <t>evaluacionID</t>
+  </si>
+  <si>
     <t>,"988059504"</t>
-  </si>
-  <si>
-    <t>usuarioID</t>
-  </si>
-  <si>
-    <t>evaluacionID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,26 +285,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -310,7 +319,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -607,233 +616,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7BBA90-A0F8-40CB-A6C3-BE1C71CAB242}">
   <dimension ref="A1:O19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="N1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="N7" t="s">
         <v>19</v>
       </c>
-      <c r="N2" t="s">
+    </row>
+    <row r="8" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" t="s">
+    <row r="14" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
         <v>38</v>
       </c>
-      <c r="O3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="N14" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="O14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="N17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
         <v>23</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="N11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="N12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="N14" t="s">
-        <v>47</v>
-      </c>
-      <c r="O14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="N17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="N18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
       </c>
       <c r="N19" t="s">
         <v>51</v>
@@ -847,84 +856,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC28EE04-5903-4CCC-A501-CB8AA8E10511}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="4" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="7">
+        <v>58</v>
+      </c>
+      <c r="B9" s="5">
         <v>66423</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>34</v>
+      <c r="B10" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
